--- a/output/reports/cv_experiment_RandomForest_qcut_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_qcut_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>17.64760327339172</v>
+        <v>4.308979749679565</v>
       </c>
       <c r="E2" t="n">
-        <v>0.999988388422108</v>
+        <v>0.9904659087366614</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999905191874167</v>
+        <v>0.9914582131506589</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5479177221576782</v>
+        <v>1.821308353709625</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04730246864744439</v>
+        <v>1.215554266843641</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,93 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>30.73723268508911</v>
+        <v>2.475330591201782</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999911915977645</v>
+        <v>0.9909618791532709</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999905232810122</v>
+        <v>0.9914582131506589</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5477994202862353</v>
+        <v>1.821308353709625</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04703679656408302</v>
+        <v>1.215554266843641</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_depth': None}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>61.86629223823547</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9999921141350498</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9999905232810122</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.5477994202862353</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.04703679656408302</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_depth': None}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>96.10405707359314</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9999925725862496</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9999905232810122</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.5477994202862353</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.04703679656408302</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_depth': None}</t>
+          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -627,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>17.64760327339172</v>
+        <v>4.308979749679565</v>
       </c>
       <c r="E2" t="n">
-        <v>0.999988388422108</v>
+        <v>0.9904659087366614</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999905191874167</v>
+        <v>0.9914582131506589</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5479177221576782</v>
+        <v>1.821308353709625</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04730246864744439</v>
+        <v>1.215554266843641</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -727,93 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>30.73723268508911</v>
+        <v>2.475330591201782</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999911915977645</v>
+        <v>0.9909618791532709</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999905232810122</v>
+        <v>0.9914582131506589</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5477994202862353</v>
+        <v>1.821308353709625</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04703679656408302</v>
+        <v>1.215554266843641</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_depth': None}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>61.86629223823547</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9999921141350498</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9999905232810122</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.5477994202862353</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.04703679656408302</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_depth': None}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>96.10405707359314</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9999925725862496</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9999905232810122</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.5477994202862353</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.04703679656408302</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_depth': None}</t>
+          <t>{'n_estimators': 49, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_depth': None}</t>
         </is>
       </c>
     </row>
